--- a/AAII_Financials/Yearly/USEA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/USEA_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="92">
   <si>
     <t>USEA</t>
   </si>
@@ -1839,8 +1839,8 @@
       <c r="I41" s="3">
         <v>400</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+      <c r="J41" s="3">
+        <v>1600</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1917,8 +1917,8 @@
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+      <c r="J43" s="3">
+        <v>500</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1956,8 +1956,8 @@
       <c r="I44" s="3">
         <v>100</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
+      <c r="J44" s="3">
+        <v>100</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
@@ -2034,8 +2034,8 @@
       <c r="I46" s="3">
         <v>500</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+      <c r="J46" s="3">
+        <v>2200</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -2112,8 +2112,8 @@
       <c r="I48" s="3">
         <v>13000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+      <c r="J48" s="3">
+        <v>13800</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -2151,8 +2151,8 @@
       <c r="I49" s="3">
         <v>0</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2346,8 +2346,8 @@
       <c r="I54" s="3">
         <v>13900</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+      <c r="J54" s="3">
+        <v>16700</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2419,8 +2419,8 @@
       <c r="I57" s="3">
         <v>100</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+      <c r="J57" s="3">
+        <v>2100</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2458,8 +2458,8 @@
       <c r="I58" s="3">
         <v>700</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+      <c r="J58" s="3">
+        <v>10300</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2536,8 +2536,8 @@
       <c r="I60" s="3">
         <v>1200</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+      <c r="J60" s="3">
+        <v>12400</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2770,8 +2770,8 @@
       <c r="I66" s="3">
         <v>6600</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+      <c r="J66" s="3">
+        <v>12400</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2982,8 +2982,8 @@
       <c r="I72" s="3">
         <v>-3000</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+      <c r="J72" s="3">
+        <v>-4100</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -3138,8 +3138,8 @@
       <c r="I76" s="3">
         <v>7300</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+      <c r="J76" s="3">
+        <v>4300</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
